--- a/codex/bundles/cognitive-memory-followup-lb4u-validation-refactor/checklists/cognitive-memory-followup-control.xlsx
+++ b/codex/bundles/cognitive-memory-followup-lb4u-validation-refactor/checklists/cognitive-memory-followup-control.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R1582768990584e85"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase Gates" sheetId="2" r:id="Rba725caef9d747e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="3" r:id="Rd27a7d8e42b645a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LB4U Stages" sheetId="4" r:id="R3f6f641d09b642d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Memory Probes" sheetId="5" r:id="R49f9d16bd68b4276"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation Matrix" sheetId="6" r:id="R413107d0f9a04c7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Refactor Targets" sheetId="7" r:id="Re67b93192b78488d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="8" r:id="R1b28c99feada45db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Log" sheetId="9" r:id="R70faa5d6620145aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="References" sheetId="10" r:id="R8a8305505974473e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rf9e4c4733d894861"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase Gates" sheetId="2" r:id="R7176f0346fce46a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="3" r:id="R8129eed2e5404f83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LB4U Stages" sheetId="4" r:id="Ra53a7ef92d514c84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Memory Probes" sheetId="5" r:id="R81387d5a45da4454"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation Matrix" sheetId="6" r:id="R05f08a28157c4da1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Refactor Targets" sheetId="7" r:id="R733f336574b34d99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="8" r:id="Rc7aef3da5f1a414e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Log" sheetId="9" r:id="Rb0c8422273a644d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="References" sheetId="10" r:id="R8c4c524836404e05"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -385,7 +385,7 @@
       </x:c>
       <x:c r="C8" s="4" t="n">
         <x:f>COUNTIF('Phase Gates'!D2:D12,"&lt;&gt;Completed")</x:f>
-        <x:v>11</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="4" t="str">
         <x:v>0</x:v>
@@ -406,7 +406,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D9" s="4" t="str">
-        <x:v>0 unresolved</x:v>
+        <x:v>Tracked and mitigated</x:v>
       </x:c>
       <x:c r="E9" s="4" t="str">
         <x:v>High risks need owner and mitigation.</x:v>
@@ -421,7 +421,7 @@
       </x:c>
       <x:c r="C10" s="4" t="n">
         <x:f>COUNTA('Evidence Log'!A2:A100)</x:f>
-        <x:v>1</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D10" s="4" t="str">
         <x:v>All gates</x:v>
@@ -608,7 +608,7 @@
         <x:v>Bundle prepared</x:v>
       </x:c>
       <x:c r="D2" s="4" t="str">
-        <x:v>Ready</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="E2" s="4" t="str">
         <x:v>Baseline recorded</x:v>
@@ -628,7 +628,7 @@
         <x:v>00 complete</x:v>
       </x:c>
       <x:c r="D3" s="4" t="str">
-        <x:v>Ready</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="E3" s="4" t="str">
         <x:v>Refactor map approved</x:v>
@@ -648,7 +648,7 @@
         <x:v>00 complete</x:v>
       </x:c>
       <x:c r="D4" s="4" t="str">
-        <x:v>Ready</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="E4" s="4" t="str">
         <x:v>Manifest and exclusions pass</x:v>
@@ -668,7 +668,7 @@
         <x:v>01 complete</x:v>
       </x:c>
       <x:c r="D5" s="4" t="str">
-        <x:v>Ready</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="E5" s="4" t="str">
         <x:v>OpenAI/Ollama roles explicit</x:v>
@@ -688,7 +688,7 @@
         <x:v>02 and 03 complete</x:v>
       </x:c>
       <x:c r="D6" s="4" t="str">
-        <x:v>Ready</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="E6" s="4" t="str">
         <x:v>Source-backed candidates pass</x:v>
@@ -708,7 +708,7 @@
         <x:v>04 complete</x:v>
       </x:c>
       <x:c r="D7" s="4" t="str">
-        <x:v>Ready</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="E7" s="4" t="str">
         <x:v>Coverage proposals pass</x:v>
@@ -728,7 +728,7 @@
         <x:v>04 complete</x:v>
       </x:c>
       <x:c r="D8" s="4" t="str">
-        <x:v>Ready</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="E8" s="4" t="str">
         <x:v>Probe improvement pass</x:v>
@@ -748,7 +748,7 @@
         <x:v>01 and 04 complete</x:v>
       </x:c>
       <x:c r="D9" s="4" t="str">
-        <x:v>Ready</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="E9" s="4" t="str">
         <x:v>Refactor tests pass</x:v>
@@ -768,7 +768,7 @@
         <x:v>05 and 06 complete</x:v>
       </x:c>
       <x:c r="D10" s="4" t="str">
-        <x:v>Ready</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="E10" s="4" t="str">
         <x:v>OpenAI multi-cycle pass</x:v>
@@ -788,7 +788,7 @@
         <x:v>08 complete</x:v>
       </x:c>
       <x:c r="D11" s="4" t="str">
-        <x:v>Ready</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="E11" s="4" t="str">
         <x:v>Local model pass or actionable block</x:v>
@@ -808,7 +808,7 @@
         <x:v>07 and 09 complete</x:v>
       </x:c>
       <x:c r="D12" s="4" t="str">
-        <x:v>Ready</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="E12" s="4" t="str">
         <x:v>Completed validator pass</x:v>
@@ -866,7 +866,7 @@
         <x:v>00,04,06</x:v>
       </x:c>
       <x:c r="D2" s="4" t="str">
-        <x:v>Ready</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="E2" s="4" t="str">
         <x:v>Invariant checklist and tests</x:v>
@@ -883,7 +883,7 @@
         <x:v>02</x:v>
       </x:c>
       <x:c r="D3" s="4" t="str">
-        <x:v>Ready</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="E3" s="4" t="str">
         <x:v>Manifest and workbook stage sheet</x:v>
@@ -900,7 +900,7 @@
         <x:v>02,08,09</x:v>
       </x:c>
       <x:c r="D4" s="4" t="str">
-        <x:v>Ready</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="E4" s="4" t="str">
         <x:v>Absence checks</x:v>
@@ -917,7 +917,7 @@
         <x:v>04</x:v>
       </x:c>
       <x:c r="D5" s="4" t="str">
-        <x:v>Ready</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="E5" s="4" t="str">
         <x:v>Candidate quality tests</x:v>
@@ -934,7 +934,7 @@
         <x:v>05</x:v>
       </x:c>
       <x:c r="D6" s="4" t="str">
-        <x:v>Ready</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="E6" s="4" t="str">
         <x:v>Scan reports</x:v>
@@ -951,7 +951,7 @@
         <x:v>06</x:v>
       </x:c>
       <x:c r="D7" s="4" t="str">
-        <x:v>Ready</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="E7" s="4" t="str">
         <x:v>Probe observation records</x:v>
@@ -968,7 +968,7 @@
         <x:v>08</x:v>
       </x:c>
       <x:c r="D8" s="4" t="str">
-        <x:v>Ready</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="E8" s="4" t="str">
         <x:v>Model profile evidence</x:v>
@@ -985,7 +985,7 @@
         <x:v>09</x:v>
       </x:c>
       <x:c r="D9" s="4" t="str">
-        <x:v>Ready</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="E9" s="4" t="str">
         <x:v>Provider and probe evidence</x:v>
@@ -1002,7 +1002,7 @@
         <x:v>03</x:v>
       </x:c>
       <x:c r="D10" s="4" t="str">
-        <x:v>Ready</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="E10" s="4" t="str">
         <x:v>Settings and operation metadata tests</x:v>
@@ -1019,7 +1019,7 @@
         <x:v>07</x:v>
       </x:c>
       <x:c r="D11" s="4" t="str">
-        <x:v>Ready</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="E11" s="4" t="str">
         <x:v>Before/after inventory and tests</x:v>
@@ -1036,7 +1036,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D12" s="4" t="str">
-        <x:v>Ready</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="E12" s="4" t="str">
         <x:v>Docs and skill diff</x:v>
@@ -1053,7 +1053,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D13" s="4" t="str">
-        <x:v>Ready</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="E13" s="4" t="str">
         <x:v>Final workbook</x:v>
@@ -1118,7 +1118,7 @@
         <x:v>What is LB4U and who is it for?</x:v>
       </x:c>
       <x:c r="F2" s="4" t="str">
-        <x:v>Ready</x:v>
+        <x:v>Completed</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="31.5" customHeight="1">
@@ -1138,7 +1138,7 @@
         <x:v>How does the button-to-staff workflow work?</x:v>
       </x:c>
       <x:c r="F3" s="4" t="str">
-        <x:v>Ready</x:v>
+        <x:v>Completed</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="31.5" customHeight="1">
@@ -1158,7 +1158,7 @@
         <x:v>Which components and installation steps are planned?</x:v>
       </x:c>
       <x:c r="F4" s="4" t="str">
-        <x:v>Ready</x:v>
+        <x:v>Completed</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="31.5" customHeight="1">
@@ -1178,7 +1178,7 @@
         <x:v>Which expenses and procurement items should be tracked?</x:v>
       </x:c>
       <x:c r="F5" s="4" t="str">
-        <x:v>Ready</x:v>
+        <x:v>Completed</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="31.5" customHeight="1">
@@ -1198,7 +1198,7 @@
         <x:v>What custom engineering remains?</x:v>
       </x:c>
       <x:c r="F6" s="4" t="str">
-        <x:v>Ready</x:v>
+        <x:v>Completed</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="31.5" customHeight="1">
@@ -1218,7 +1218,7 @@
         <x:v>What are release risks and validation sites?</x:v>
       </x:c>
       <x:c r="F7" s="4" t="str">
-        <x:v>Ready</x:v>
+        <x:v>Completed</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="31.5" customHeight="1">
@@ -1238,7 +1238,7 @@
         <x:v>What should a proper business plan contain from studied sources?</x:v>
       </x:c>
       <x:c r="F8" s="4" t="str">
-        <x:v>Ready</x:v>
+        <x:v>Completed</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="31.5" customHeight="1">
@@ -1258,7 +1258,7 @@
         <x:v>Which knowledge is LB4U-specific versus reusable?</x:v>
       </x:c>
       <x:c r="F9" s="4" t="str">
-        <x:v>Ready</x:v>
+        <x:v>Completed</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1320,7 +1320,7 @@
         <x:v>OpenAI then Ollama</x:v>
       </x:c>
       <x:c r="F2" s="4" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Completed</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="31.5" customHeight="1">
@@ -1340,7 +1340,7 @@
         <x:v>OpenAI then Ollama</x:v>
       </x:c>
       <x:c r="F3" s="4" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Completed</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="31.5" customHeight="1">
@@ -1360,7 +1360,7 @@
         <x:v>OpenAI then Ollama</x:v>
       </x:c>
       <x:c r="F4" s="4" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Completed</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="31.5" customHeight="1">
@@ -1380,7 +1380,7 @@
         <x:v>OpenAI then Ollama</x:v>
       </x:c>
       <x:c r="F5" s="4" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Completed</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="31.5" customHeight="1">
@@ -1400,7 +1400,7 @@
         <x:v>OpenAI then Ollama</x:v>
       </x:c>
       <x:c r="F6" s="4" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Completed</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="31.5" customHeight="1">
@@ -1420,7 +1420,7 @@
         <x:v>OpenAI</x:v>
       </x:c>
       <x:c r="F7" s="4" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Completed</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="31.5" customHeight="1">
@@ -1440,7 +1440,7 @@
         <x:v>OpenAI</x:v>
       </x:c>
       <x:c r="F8" s="4" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Completed</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="31.5" customHeight="1">
@@ -1460,7 +1460,7 @@
         <x:v>OpenAI then Ollama</x:v>
       </x:c>
       <x:c r="F9" s="4" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Completed</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1517,7 +1517,7 @@
         <x:v>operation ids, source-backed answers, snapshot delta</x:v>
       </x:c>
       <x:c r="F2" s="4" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Completed</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="31.5" customHeight="1">
@@ -1537,7 +1537,7 @@
         <x:v>candidate records, accepted/rejected reviews</x:v>
       </x:c>
       <x:c r="F3" s="4" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Completed</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="31.5" customHeight="1">
@@ -1557,7 +1557,7 @@
         <x:v>before/after probe summaries, gap closure</x:v>
       </x:c>
       <x:c r="F4" s="4" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Completed</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="31.5" customHeight="1">
@@ -1577,7 +1577,7 @@
         <x:v>model status, max output tokens, truncation state</x:v>
       </x:c>
       <x:c r="F5" s="4" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Completed</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="31.5" customHeight="1">
@@ -1597,7 +1597,7 @@
         <x:v>test outputs, completed bundle validator, workbook final</x:v>
       </x:c>
       <x:c r="F6" s="4" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Completed</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1988,9 +1988,369 @@
         <x:v>Completed</x:v>
       </x:c>
     </x:row>
+    <x:row r="3" ht="31.5" customHeight="1">
+      <x:c r="A3" s="4" t="str">
+        <x:v>2026-05-18</x:v>
+      </x:c>
+      <x:c r="B3" s="4" t="str">
+        <x:v>00</x:v>
+      </x:c>
+      <x:c r="C3" s="4" t="str">
+        <x:v>Worktree</x:v>
+      </x:c>
+      <x:c r="D3" s="4" t="str">
+        <x:v>git status --short</x:v>
+      </x:c>
+      <x:c r="E3" s="4" t="str">
+        <x:v>Only follow-up bundle is untracked and owned by this workflow.</x:v>
+      </x:c>
+      <x:c r="F3" s="4" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="31.5" customHeight="1">
+      <x:c r="A4" s="4" t="str">
+        <x:v>2026-05-18</x:v>
+      </x:c>
+      <x:c r="B4" s="4" t="str">
+        <x:v>00</x:v>
+      </x:c>
+      <x:c r="C4" s="4" t="str">
+        <x:v>Unit tests</x:v>
+      </x:c>
+      <x:c r="D4" s="4" t="str">
+        <x:v>dotnet test Unit --filter FullyQualifiedName~CognitiveMemory -m:1</x:v>
+      </x:c>
+      <x:c r="E4" s="4" t="str">
+        <x:v>Passed 104/104.</x:v>
+      </x:c>
+      <x:c r="F4" s="4" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="31.5" customHeight="1">
+      <x:c r="A5" s="4" t="str">
+        <x:v>2026-05-18</x:v>
+      </x:c>
+      <x:c r="B5" s="4" t="str">
+        <x:v>00</x:v>
+      </x:c>
+      <x:c r="C5" s="4" t="str">
+        <x:v>Integration tests</x:v>
+      </x:c>
+      <x:c r="D5" s="4" t="str">
+        <x:v>dotnet test Integration --filter FullyQualifiedName~CognitiveMemory -m:1</x:v>
+      </x:c>
+      <x:c r="E5" s="4" t="str">
+        <x:v>Failed 1/25 on SQLite DateTimeOffset ORDER BY in recall lexical candidate query.</x:v>
+      </x:c>
+      <x:c r="F5" s="4" t="str">
+        <x:v>Needs Repair</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="31.5" customHeight="1">
+      <x:c r="A6" s="4" t="str">
+        <x:v>2026-05-18</x:v>
+      </x:c>
+      <x:c r="B6" s="4" t="str">
+        <x:v>00</x:v>
+      </x:c>
+      <x:c r="C6" s="4" t="str">
+        <x:v>Component tests</x:v>
+      </x:c>
+      <x:c r="D6" s="4" t="str">
+        <x:v>dotnet test Components --filter FullyQualifiedName~CognitiveMemory -m:1</x:v>
+      </x:c>
+      <x:c r="E6" s="4" t="str">
+        <x:v>Passed 1/1.</x:v>
+      </x:c>
+      <x:c r="F6" s="4" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="31.5" customHeight="1">
+      <x:c r="A7" s="4" t="str">
+        <x:v>2026-05-18</x:v>
+      </x:c>
+      <x:c r="B7" s="4" t="str">
+        <x:v>00</x:v>
+      </x:c>
+      <x:c r="C7" s="4" t="str">
+        <x:v>API readiness</x:v>
+      </x:c>
+      <x:c r="D7" s="4" t="str">
+        <x:v>Get-NetTCPConnection default ports</x:v>
+      </x:c>
+      <x:c r="E7" s="4" t="str">
+        <x:v>No listener on 5032 or 7271; live API validation must start web app later.</x:v>
+      </x:c>
+      <x:c r="F7" s="4" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="31.5" customHeight="1">
+      <x:c r="A8" s="4" t="str">
+        <x:v>2026-05-18</x:v>
+      </x:c>
+      <x:c r="B8" s="4" t="str">
+        <x:v>01</x:v>
+      </x:c>
+      <x:c r="C8" s="4" t="str">
+        <x:v>Recall fix</x:v>
+      </x:c>
+      <x:c r="D8" s="4" t="str">
+        <x:v>dotnet test Integration --filter FullyQualifiedName~CognitiveMemory -m:1</x:v>
+      </x:c>
+      <x:c r="E8" s="4" t="str">
+        <x:v>SQLite DateTimeOffset ordering failure repaired; final integration pass 25/25.</x:v>
+      </x:c>
+      <x:c r="F8" s="4" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="31.5" customHeight="1">
+      <x:c r="A9" s="4" t="str">
+        <x:v>2026-05-18</x:v>
+      </x:c>
+      <x:c r="B9" s="4" t="str">
+        <x:v>02</x:v>
+      </x:c>
+      <x:c r="C9" s="4" t="str">
+        <x:v>Secret safety</x:v>
+      </x:c>
+      <x:c r="D9" s="4" t="str">
+        <x:v>CognitiveMemoryOperationalSettingsTests</x:v>
+      </x:c>
+      <x:c r="E9" s="4" t="str">
+        <x:v>Staged manifest validates exclusions without reading excluded paths.</x:v>
+      </x:c>
+      <x:c r="F9" s="4" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="31.5" customHeight="1">
+      <x:c r="A10" s="4" t="str">
+        <x:v>2026-05-18</x:v>
+      </x:c>
+      <x:c r="B10" s="4" t="str">
+        <x:v>03</x:v>
+      </x:c>
+      <x:c r="C10" s="4" t="str">
+        <x:v>Settings</x:v>
+      </x:c>
+      <x:c r="D10" s="4" t="str">
+        <x:v>GET/PUT /api/cognitive-memory/settings</x:v>
+      </x:c>
+      <x:c r="E10" s="4" t="str">
+        <x:v>OpenAI gpt-5-mini and Ollama gptoss20b64k profiles read back with explicit output token budgets.</x:v>
+      </x:c>
+      <x:c r="F10" s="4" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="31.5" customHeight="1">
+      <x:c r="A11" s="4" t="str">
+        <x:v>2026-05-18</x:v>
+      </x:c>
+      <x:c r="B11" s="4" t="str">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c r="C11" s="4" t="str">
+        <x:v>Consolidation</x:v>
+      </x:c>
+      <x:c r="D11" s="4" t="str">
+        <x:v>POST /api/cognitive-memory/consolidation/runs</x:v>
+      </x:c>
+      <x:c r="E11" s="4" t="str">
+        <x:v>Run 27301740-2154-48f0-b98f-7b01303d95aa scanned 43, created 39 after contact filter.</x:v>
+      </x:c>
+      <x:c r="F11" s="4" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="31.5" customHeight="1">
+      <x:c r="A12" s="4" t="str">
+        <x:v>2026-05-18</x:v>
+      </x:c>
+      <x:c r="B12" s="4" t="str">
+        <x:v>05</x:v>
+      </x:c>
+      <x:c r="C12" s="4" t="str">
+        <x:v>Epistemic drive</x:v>
+      </x:c>
+      <x:c r="D12" s="4" t="str">
+        <x:v>POST /api/cognitive-memory/epistemic-drive/scans</x:v>
+      </x:c>
+      <x:c r="E12" s="4" t="str">
+        <x:v>Approved source-backed proposals; repeat scan returned 0 duplicates.</x:v>
+      </x:c>
+      <x:c r="F12" s="4" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="31.5" customHeight="1">
+      <x:c r="A13" s="4" t="str">
+        <x:v>2026-05-18</x:v>
+      </x:c>
+      <x:c r="B13" s="4" t="str">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c r="C13" s="4" t="str">
+        <x:v>Probes</x:v>
+      </x:c>
+      <x:c r="D13" s="4" t="str">
+        <x:v>POST /api/cognitive-memory/probes/sessions/{id}/turns</x:v>
+      </x:c>
+      <x:c r="E13" s="4" t="str">
+        <x:v>Probe summaries retained source context and redacted emails/phones.</x:v>
+      </x:c>
+      <x:c r="F13" s="4" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="31.5" customHeight="1">
+      <x:c r="A14" s="4" t="str">
+        <x:v>2026-05-18</x:v>
+      </x:c>
+      <x:c r="B14" s="4" t="str">
+        <x:v>08</x:v>
+      </x:c>
+      <x:c r="C14" s="4" t="str">
+        <x:v>OpenAI live validation</x:v>
+      </x:c>
+      <x:c r="D14" s="4" t="str">
+        <x:v>gpt-5-mini profiles and LB4U staged ingestion</x:v>
+      </x:c>
+      <x:c r="E14" s="4" t="str">
+        <x:v>Business-plan/product/procurement probes improved after review and extraction cycles.</x:v>
+      </x:c>
+      <x:c r="F14" s="4" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="31.5" customHeight="1">
+      <x:c r="A15" s="4" t="str">
+        <x:v>2026-05-18</x:v>
+      </x:c>
+      <x:c r="B15" s="4" t="str">
+        <x:v>09</x:v>
+      </x:c>
+      <x:c r="C15" s="4" t="str">
+        <x:v>Ollama live validation</x:v>
+      </x:c>
+      <x:c r="D15" s="4" t="str">
+        <x:v>Ollama /api/generate</x:v>
+      </x:c>
+      <x:c r="E15" s="4" t="str">
+        <x:v>gptoss20b64k accepted num_predict=8192 and local settings recall smoke passed.</x:v>
+      </x:c>
+      <x:c r="F15" s="4" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="31.5" customHeight="1">
+      <x:c r="A16" s="4" t="str">
+        <x:v>2026-05-18</x:v>
+      </x:c>
+      <x:c r="B16" s="4" t="str">
+        <x:v>Final</x:v>
+      </x:c>
+      <x:c r="C16" s="4" t="str">
+        <x:v>Unit tests</x:v>
+      </x:c>
+      <x:c r="D16" s="4" t="str">
+        <x:v>dotnet test Unit --filter FullyQualifiedName~CognitiveMemory -m:1</x:v>
+      </x:c>
+      <x:c r="E16" s="4" t="str">
+        <x:v>Passed 113/113.</x:v>
+      </x:c>
+      <x:c r="F16" s="4" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="31.5" customHeight="1">
+      <x:c r="A17" s="4" t="str">
+        <x:v>2026-05-18</x:v>
+      </x:c>
+      <x:c r="B17" s="4" t="str">
+        <x:v>Final</x:v>
+      </x:c>
+      <x:c r="C17" s="4" t="str">
+        <x:v>Integration tests</x:v>
+      </x:c>
+      <x:c r="D17" s="4" t="str">
+        <x:v>dotnet test Integration --filter FullyQualifiedName~CognitiveMemory -m:1</x:v>
+      </x:c>
+      <x:c r="E17" s="4" t="str">
+        <x:v>Passed 25/25.</x:v>
+      </x:c>
+      <x:c r="F17" s="4" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="31.5" customHeight="1">
+      <x:c r="A18" s="4" t="str">
+        <x:v>2026-05-18</x:v>
+      </x:c>
+      <x:c r="B18" s="4" t="str">
+        <x:v>Final</x:v>
+      </x:c>
+      <x:c r="C18" s="4" t="str">
+        <x:v>Component tests</x:v>
+      </x:c>
+      <x:c r="D18" s="4" t="str">
+        <x:v>dotnet test Components --filter FullyQualifiedName~CognitiveMemory -m:1</x:v>
+      </x:c>
+      <x:c r="E18" s="4" t="str">
+        <x:v>Passed 1/1.</x:v>
+      </x:c>
+      <x:c r="F18" s="4" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="31.5" customHeight="1">
+      <x:c r="A19" s="4" t="str">
+        <x:v>2026-05-18</x:v>
+      </x:c>
+      <x:c r="B19" s="4" t="str">
+        <x:v>Final</x:v>
+      </x:c>
+      <x:c r="C19" s="4" t="str">
+        <x:v>Build</x:v>
+      </x:c>
+      <x:c r="D19" s="4" t="str">
+        <x:v>dotnet build CanDoItAll.slnx --no-restore -m:1 --verbosity:minimal</x:v>
+      </x:c>
+      <x:c r="E19" s="4" t="str">
+        <x:v>Passed with existing Google.Protobuf MSB3277 warnings.</x:v>
+      </x:c>
+      <x:c r="F19" s="4" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="31.5" customHeight="1">
+      <x:c r="A20" s="4" t="str">
+        <x:v>2026-05-18</x:v>
+      </x:c>
+      <x:c r="B20" s="4" t="str">
+        <x:v>Final</x:v>
+      </x:c>
+      <x:c r="C20" s="4" t="str">
+        <x:v>Bundle validator</x:v>
+      </x:c>
+      <x:c r="D20" s="4" t="str">
+        <x:v>validate_bundle.py --profile initiative --stage completed</x:v>
+      </x:c>
+      <x:c r="E20" s="4" t="str">
+        <x:v>Bundle is valid for stage completed.</x:v>
+      </x:c>
+      <x:c r="F20" s="4" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="F2">
+    <x:dataValidation type="list" sqref="F2:F20">
       <x:formula1>"Ready,In Progress,Completed,Blocked,Needs Repair,Pending"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
